--- a/output/matrixify_create_large_merge.xlsx
+++ b/output/matrixify_create_large_merge.xlsx
@@ -413,9 +413,7767 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AA61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Handle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Variant Command</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Variant SKU</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Variant Barcode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Variant Price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Variant Compare At Price</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Variant Cost</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Variant Weight</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Variant Weight Unit</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Variant Inventory Tracker</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Variant Inventory Policy</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Variant Inventory Qty</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Variant Fulfillment Service</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Variant Requires Shipping</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Variant Taxable</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Variant Image</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Google Shopping / MPN</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Google Shopping / Condition</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Variant Metafield: custom.sku [single_line_text_field]</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Variant Metafield: custom.produktinfo [multi_line_text_field]</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Variant Metafield: custom.variantbilleder [list.single_line_text_field]</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Option1 Name</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Option1 Value</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Option2 Name</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Option2 Value</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Option3 Name</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Option3 Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3127458</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8720287413349</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2849</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3799</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1663</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41050</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>21</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413349_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3127458</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3127458</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 83 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 80 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 80 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413349_m_en_hd_1.jpg, https://vdxl.im/8720287413349_a_en_hd_1.jpg, https://vdxl.im/8720287413349_g_en_hd_1.jpg, https://vdxl.im/8720287413349_g_en_hd_2.jpg, https://vdxl.im/8720287413349_g_en_hd_3.jpg, https://vdxl.im/8720287413349_g_en_hd_4.jpg, https://vdxl.im/8720287413349_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>80 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3127459</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8720287413356</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2909</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3879</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1699</v>
+      </c>
+      <c r="H3" t="n">
+        <v>41090</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>18</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413356_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3127459</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3127459</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 83 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og sort&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 80 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 80 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413356_m_en_hd_1.jpg, https://vdxl.im/8720287413356_a_en_hd_1.jpg, https://vdxl.im/8720287413356_g_en_hd_1.jpg, https://vdxl.im/8720287413356_g_en_hd_2.jpg, https://vdxl.im/8720287413356_g_en_hd_3.jpg, https://vdxl.im/8720287413356_g_en_hd_4.jpg, https://vdxl.im/8720287413356_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>80 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3127469</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8720287413455</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2929</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3909</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1709</v>
+      </c>
+      <c r="H4" t="n">
+        <v>44660</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>109</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413455_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3127469</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3127469</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 93 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413455_m_en_hd_1.jpg, https://vdxl.im/8720287413455_a_en_hd_1.jpg, https://vdxl.im/8720287413455_g_en_hd_1.jpg, https://vdxl.im/8720287413455_g_en_hd_2.jpg, https://vdxl.im/8720287413455_g_en_hd_3.jpg, https://vdxl.im/8720287413455_g_en_hd_4.jpg, https://vdxl.im/8720287413455_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3127470</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8720287413462</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3019</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4029</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1765</v>
+      </c>
+      <c r="H5" t="n">
+        <v>45120</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>119</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413462_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3127470</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3127470</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 93 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413462_m_en_hd_1.jpg, https://vdxl.im/8720287413462_a_en_hd_1.jpg, https://vdxl.im/8720287413462_g_en_hd_1.jpg, https://vdxl.im/8720287413462_g_en_hd_2.jpg, https://vdxl.im/8720287413462_g_en_hd_3.jpg, https://vdxl.im/8720287413462_g_en_hd_4.jpg, https://vdxl.im/8720287413462_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3127471</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8720287413479</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3829</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1674</v>
+      </c>
+      <c r="H6" t="n">
+        <v>44500</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>51</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413479_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3127471</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3127471</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 93 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og sort&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413479_m_en_hd_1.jpg, https://vdxl.im/8720287413479_a_en_hd_1.jpg, https://vdxl.im/8720287413479_g_en_hd_1.jpg, https://vdxl.im/8720287413479_g_en_hd_2.jpg, https://vdxl.im/8720287413479_g_en_hd_3.jpg, https://vdxl.im/8720287413479_g_en_hd_4.jpg, https://vdxl.im/8720287413479_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3127475</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8720287413516</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3029</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4039</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1772</v>
+      </c>
+      <c r="H7" t="n">
+        <v>46510</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>99</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413516_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3127475</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3127475</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 103 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 100 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 100 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413516_m_en_hd_1.jpg, https://vdxl.im/8720287413516_a_en_hd_1.jpg, https://vdxl.im/8720287413516_g_en_hd_1.jpg, https://vdxl.im/8720287413516_g_en_hd_2.jpg, https://vdxl.im/8720287413516_g_en_hd_3.jpg, https://vdxl.im/8720287413516_g_en_hd_4.jpg, https://vdxl.im/8720287413516_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>100 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3127487</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8720287413639</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4419</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5899</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2581</v>
+      </c>
+      <c r="H8" t="n">
+        <v>62190</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>106</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413639_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3127487</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3127487</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 193 x 147 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413639_m_en_hd_1.jpg, https://vdxl.im/8720287413639_a_en_hd_1.jpg, https://vdxl.im/8720287413639_g_en_hd_1.jpg, https://vdxl.im/8720287413639_g_en_hd_2.jpg, https://vdxl.im/8720287413639_g_en_hd_3.jpg, https://vdxl.im/8720287413639_g_en_hd_4.jpg, https://vdxl.im/8720287413639_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3127488</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8720287413646</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4039</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5389</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2361</v>
+      </c>
+      <c r="H9" t="n">
+        <v>61430</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>168</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413646_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3127488</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3127488</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 193 x 147 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413646_m_en_hd_1.jpg, https://vdxl.im/8720287413646_a_en_hd_1.jpg, https://vdxl.im/8720287413646_g_en_hd_1.jpg, https://vdxl.im/8720287413646_g_en_hd_2.jpg, https://vdxl.im/8720287413646_g_en_hd_3.jpg, https://vdxl.im/8720287413646_g_en_hd_4.jpg, https://vdxl.im/8720287413646_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3127489</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8720287413653</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4329</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5779</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2531</v>
+      </c>
+      <c r="H10" t="n">
+        <v>61430</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413653_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3127489</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3127489</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 193 x 147 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og sort&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413653_m_en_hd_1.jpg, https://vdxl.im/8720287413653_a_en_hd_1.jpg, https://vdxl.im/8720287413653_g_en_hd_1.jpg, https://vdxl.im/8720287413653_g_en_hd_2.jpg, https://vdxl.im/8720287413653_g_en_hd_3.jpg, https://vdxl.im/8720287413653_g_en_hd_4.jpg, https://vdxl.im/8720287413653_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3127494</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8720287413707</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4149</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5539</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2424</v>
+      </c>
+      <c r="H11" t="n">
+        <v>63350</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>168</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413707_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3127494</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3127494</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 147 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 140 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 140 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413707_m_en_hd_1.jpg, https://vdxl.im/8720287413707_a_en_hd_1.jpg, https://vdxl.im/8720287413707_g_en_hd_1.jpg, https://vdxl.im/8720287413707_g_en_hd_2.jpg, https://vdxl.im/8720287413707_g_en_hd_3.jpg, https://vdxl.im/8720287413707_g_en_hd_4.jpg, https://vdxl.im/8720287413707_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>140 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3127495</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8720287413714</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4439</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5919</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2591</v>
+      </c>
+      <c r="H12" t="n">
+        <v>63470</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>50</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413714_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3127495</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3127495</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 147 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og sort&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 140 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 140 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413714_m_en_hd_1.jpg, https://vdxl.im/8720287413714_a_en_hd_1.jpg, https://vdxl.im/8720287413714_g_en_hd_1.jpg, https://vdxl.im/8720287413714_g_en_hd_2.jpg, https://vdxl.im/8720287413714_g_en_hd_3.jpg, https://vdxl.im/8720287413714_g_en_hd_4.jpg, https://vdxl.im/8720287413714_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>140 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3127500</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8720287413769</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4599</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6139</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2687</v>
+      </c>
+      <c r="H13" t="n">
+        <v>69770</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>100</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413769_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3127500</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3127500</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 163 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 160 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 160 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413769_m_en_hd_1.jpg, https://vdxl.im/8720287413769_a_en_hd_1.jpg, https://vdxl.im/8720287413769_g_en_hd_1.jpg, https://vdxl.im/8720287413769_g_en_hd_2.jpg, https://vdxl.im/8720287413769_g_en_hd_3.jpg, https://vdxl.im/8720287413769_g_en_hd_4.jpg, https://vdxl.im/8720287413769_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>160 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3127505</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8720287413813</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4799</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6399</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2807</v>
+      </c>
+      <c r="H14" t="n">
+        <v>72870</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>103</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413813_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3127505</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3127505</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 183x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 180 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 180 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413813_m_en_hd_1.jpg, https://vdxl.im/8720287413813_a_en_hd_1.jpg, https://vdxl.im/8720287413813_g_en_hd_1.jpg, https://vdxl.im/8720287413813_g_en_hd_2.jpg, https://vdxl.im/8720287413813_g_en_hd_3.jpg, https://vdxl.im/8720287413813_g_en_hd_4.jpg, https://vdxl.im/8720287413813_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3127506</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8720287413820</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4969</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6629</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2906</v>
+      </c>
+      <c r="H15" t="n">
+        <v>72530</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>111</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413820_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3127506</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3127506</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 183x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål: 180 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 180 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413820_m_en_hd_1.jpg, https://vdxl.im/8720287413820_a_en_hd_1.jpg, https://vdxl.im/8720287413820_g_en_hd_1.jpg, https://vdxl.im/8720287413820_g_en_hd_2.jpg, https://vdxl.im/8720287413820_g_en_hd_3.jpg, https://vdxl.im/8720287413820_g_en_hd_4.jpg, https://vdxl.im/8720287413820_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3127511</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8720287413875</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5359</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7149</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3131</v>
+      </c>
+      <c r="H16" t="n">
+        <v>82340</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>86</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413875_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3127511</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3127511</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Du kan nyde en god nattesøvn ved hjælp af denne kontinentalseng! Den tilbyder maksimal afslapning og en god søvn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blød fløjl: Fløjl er et blødt og luksuriøst stof, der er kendetegnet ved dets tætte og jævne fibre. Fløjlsstof er blødt og komfortabelt at røre ved.&lt;/li&gt;&lt;li&gt;Praktisk sengegavl: Sengegavlen kan justeres i højden efter behov. Den giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Madras med pocketfjedre: De indbyggede, individuelle pocketfjedre er kendt for deres yderst høje kvalitet, og de sikrer høj holdbarhed og en stor tilpasningsevne. De kan effektivt absorbere støj og stød, der opstår, når man vender og drejer sig.&lt;/li&gt;&lt;li&gt;Mellemhård støtte: Madrassen giver øget stabilitet på perfekt vis samt den rette fasthed uden at gå på kompromis med komforten. Den er derfor ideel til dem, der sover på maven.&lt;/li&gt;&lt;li&gt;Hudvenlig topmadras: Madrasbeskytteren har et slidstærkt og hudvenligt stofbetræk, hvilket gør den blød og komfortabel.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Seng:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), massivt lærketræ, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 203 x 203 x 78/88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid og lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Pocketfjedre, skum&lt;/li&gt;&lt;li&gt;Mål, hver: 100 x 200 x 20 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Topmadras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Mål: 200 x 200 x 5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegavl med kanter&lt;/li&gt;&lt;li&gt;2 x madras&lt;/li&gt;&lt;li&gt;1 x topmadras&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287413875_m_en_hd_1.jpg, https://vdxl.im/8720287413875_a_en_hd_1.jpg, https://vdxl.im/8720287413875_g_en_hd_1.jpg, https://vdxl.im/8720287413875_g_en_hd_2.jpg, https://vdxl.im/8720287413875_g_en_hd_3.jpg, https://vdxl.im/8720287413875_g_en_hd_4.jpg, https://vdxl.im/8720287413875_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>200 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Blok med firkanter</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>box-spring-seng-med-madras-moerkegraa-80x200-cm-floejl-lysegraa-2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3340454</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8721158225016</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4909</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6549</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2867</v>
+      </c>
+      <c r="H17" t="n">
+        <v>73620</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158225016_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3340454</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3340454</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne flotte Box Spring-seng kombinerer moderne stil med komfort og har en blød fløjlsoverflade, der handler om at slappe af. Den er lavet til dagens minimalistiske boligejer med en slank profil, der passer perfekt ind i et trendy soveværelse. Den justerbare sengegavl tilføjer en praktisk dimension, så du kan tilpasse den til dine behov. Den afdæmpede mørkegrå farve passer super godt til forskellige indretningsstile og skaber en klassisk stemning, der gør dit soveværelse til et fredfyldt sted.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen er lavet af en solid træramme dækket af lækkert fløjl, som giver den en blød berøring og et flot look. Den robuste konstruktion sikrer langvarig støtte, og fløjlsfinishen tilføjer et elegant touch til dit soveværelse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en støttende madras og topper for fantastisk komfort. Den justerbare sengegavl er lavet af skum og massivt fyrretræ, som giver ekstra støtte til nakke og ryg. Den har sorte plastben for stabilitet, der passer godt til det moderne look.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner / Funktion / Design:&lt;/b&gt; Med en justerbar sengegavl kan du tilpasse den manuelt, så den passer til din komfort. Sengen blander moderne design med praktisk anvendelse, hvilket gør den til et sjovt element i enhver stilfuld soveværelsesopsætning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Fantastisk til moderne soveværelser, hvor sengen tilbyder et indbydende sted at slappe af. Den tilpasselige sengegavl giver dig mulighed for at justere komforten, hvilket er perfekt for dem, der elsker at læse eller se tv i sengen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; Hold sengen pæn ved at støve den af med en blød, tør klud. Undgå hårde rengøringsmidler for at beskytte fløjlsoverfladen, så sengen forbliver indbydende, som den dag du satte den op.&lt;/li&gt;&lt;/ul&gt; &lt;p&gt;&lt;strong&gt;Godt at vide:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Denne sengestel har et lamelbund-design og inkluderer lamellerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Hovedgærdemateriale: Fløjl&lt;/li&gt;&lt;li&gt;Madras fasthed: Medium&lt;/li&gt;&lt;li&gt;Slutte: Blødt fløjlsstof&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 203 x 183 x 88 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Adjustable min/max dimensions: 78-88 cm&lt;/li&gt;&lt;li&gt;Madras størrelse: 180 x 200 cm&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Blød velour&lt;/li&gt;&lt;li&gt;Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1x Sengebund&lt;/li&gt;&lt;li&gt;1x Madras&lt;/li&gt;&lt;li&gt;1x Topmadras&lt;/li&gt;&lt;li&gt;1x Hovedgærde med ører&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158225016_mo-im_en_hd_1.jpg, https://vdxl.im/8721158225016_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721158225016_mo-im_en_hd_2.jpg, https://vdxl.im/8721158225016_wbg-an_en_hd_1.jpg, https://vdxl.im/8721158225016_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158225016_wbg-an_en_hd_3.jpg, https://vdxl.im/8721158225016_wbg-fr_en_hd_5.jpg, https://vdxl.im/8721158225016_wbg-si_en_hd_6.jpg, https://vdxl.im/8721158225016_detail_en_hd_1.jpg, https://vdxl.im/8721158225016_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158225016_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Diamant blokke design</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4107316</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8721158694072</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>209</v>
+      </c>
+      <c r="F18" t="n">
+        <v>299</v>
+      </c>
+      <c r="G18" t="n">
+        <v>122</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>200</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694072_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4107316</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>4107316</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694072_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694072_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158694072_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694072_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158694072_detail_en_hd_1.jpg, https://vdxl.im/8721158694072_detail_en_hd_2.jpg, https://vdxl.im/8721158694072_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694072_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Beige</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4107321</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8721158694126</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>309</v>
+      </c>
+      <c r="F19" t="n">
+        <v>449</v>
+      </c>
+      <c r="G19" t="n">
+        <v>181</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>149</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694126_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4107321</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>4107321</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694126_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694126_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158694126_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694126_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158694126_detail_en_hd_1.jpg, https://vdxl.im/8721158694126_detail_en_hd_2.jpg, https://vdxl.im/8721158694126_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694126_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4107326</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8721158694171</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>269</v>
+      </c>
+      <c r="F20" t="n">
+        <v>389</v>
+      </c>
+      <c r="G20" t="n">
+        <v>159</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>112</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694171_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>4107326</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>4107326</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lys blå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694171_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694171_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158694171_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694171_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158694171_detail_en_hd_1.jpg, https://vdxl.im/8721158694171_detail_en_hd_2.jpg, https://vdxl.im/8721158694171_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694171_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lyseblå</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4107331</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8721158694225</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>309</v>
+      </c>
+      <c r="F21" t="n">
+        <v>449</v>
+      </c>
+      <c r="G21" t="n">
+        <v>181</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>123</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694225_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>4107331</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>4107331</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694225_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694225_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158694225_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694225_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158694225_detail_en_hd_1.jpg, https://vdxl.im/8721158694225_detail_en_hd_2.jpg, https://vdxl.im/8721158694225_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694225_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4107336</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8721158694270</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>269</v>
+      </c>
+      <c r="F22" t="n">
+        <v>389</v>
+      </c>
+      <c r="G22" t="n">
+        <v>159</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>167</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694270_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>4107336</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>4107336</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørk brun&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694270_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694270_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158694270_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694270_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158694270_detail_en_hd_1.jpg, https://vdxl.im/8721158694270_detail_en_hd_2.jpg, https://vdxl.im/8721158694270_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694270_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mørkebrun</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4107341</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8721158694324</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229</v>
+      </c>
+      <c r="F23" t="n">
+        <v>329</v>
+      </c>
+      <c r="G23" t="n">
+        <v>130</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>200</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694324_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>4107341</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4107341</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracit&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694324_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694324_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158694324_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694324_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158694324_detail_en_hd_1.jpg, https://vdxl.im/8721158694324_detail_en_hd_2.jpg, https://vdxl.im/8721158694324_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694324_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Antracit</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4107346</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8721158694379</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229</v>
+      </c>
+      <c r="F24" t="n">
+        <v>329</v>
+      </c>
+      <c r="G24" t="n">
+        <v>130</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>175</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694379_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>4107346</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>4107346</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694379_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694379_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158694379_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694379_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158694379_detail_en_hd_1.jpg, https://vdxl.im/8721158694379_detail_en_hd_2.jpg, https://vdxl.im/8721158694379_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694379_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4107351</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8721158694423</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>289</v>
+      </c>
+      <c r="F25" t="n">
+        <v>419</v>
+      </c>
+      <c r="G25" t="n">
+        <v>166</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>99</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694423_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>4107351</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>4107351</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Bleg grå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694423_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694423_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158694423_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694423_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158694423_detail_en_hd_1.jpg, https://vdxl.im/8721158694423_detail_en_hd_2.jpg, https://vdxl.im/8721158694423_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694423_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lys grå</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4107356</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8721158694478</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>359</v>
+      </c>
+      <c r="F26" t="n">
+        <v>519</v>
+      </c>
+      <c r="G26" t="n">
+        <v>207</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>34</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694478_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>4107356</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>4107356</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Vinrød&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694478_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694478_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158694478_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694478_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158694478_detail_en_hd_1.jpg, https://vdxl.im/8721158694478_detail_en_hd_2.jpg, https://vdxl.im/8721158694478_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694478_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vinrød</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4107361</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8721158694522</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>269</v>
+      </c>
+      <c r="F27" t="n">
+        <v>389</v>
+      </c>
+      <c r="G27" t="n">
+        <v>157</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>78</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694522_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>4107361</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>4107361</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Metal grå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694522_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694522_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158694522_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694522_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158694522_detail_en_hd_1.jpg, https://vdxl.im/8721158694522_detail_en_hd_2.jpg, https://vdxl.im/8721158694522_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694522_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Metal grå</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4107366</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8721158694577</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>359</v>
+      </c>
+      <c r="F28" t="n">
+        <v>519</v>
+      </c>
+      <c r="G28" t="n">
+        <v>207</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>30</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694577_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>4107366</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>4107366</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørk blå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694577_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694577_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158694577_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694577_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158694577_detail_en_hd_1.jpg, https://vdxl.im/8721158694577_detail_en_hd_2.jpg, https://vdxl.im/8721158694577_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694577_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mørkeblå</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4107371</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8721158694621</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>209</v>
+      </c>
+      <c r="F29" t="n">
+        <v>299</v>
+      </c>
+      <c r="G29" t="n">
+        <v>122</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>200</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694621_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>4107371</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>4107371</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lys brun&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694621_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694621_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158694621_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694621_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158694621_detail_en_hd_1.jpg, https://vdxl.im/8721158694621_detail_en_hd_2.jpg, https://vdxl.im/8721158694621_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694621_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lysebrun</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4107376</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8721158694676</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>339</v>
+      </c>
+      <c r="F30" t="n">
+        <v>489</v>
+      </c>
+      <c r="G30" t="n">
+        <v>195</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>149</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694676_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>4107376</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4107376</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694676_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694676_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158694676_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694676_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158694676_detail_en_hd_1.jpg, https://vdxl.im/8721158694676_detail_en_hd_2.jpg, https://vdxl.im/8721158694676_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694676_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4107381</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8721158694720</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>339</v>
+      </c>
+      <c r="F31" t="n">
+        <v>489</v>
+      </c>
+      <c r="G31" t="n">
+        <v>198</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>121</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694720_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>4107381</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>4107381</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lilla&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694720_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694720_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158694720_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694720_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158694720_detail_en_hd_1.jpg, https://vdxl.im/8721158694720_detail_en_hd_2.jpg, https://vdxl.im/8721158694720_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694720_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lilla</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>4107386</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>8721158694775</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>339</v>
+      </c>
+      <c r="F32" t="n">
+        <v>489</v>
+      </c>
+      <c r="G32" t="n">
+        <v>197</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>101</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694775_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>4107386</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>4107386</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Ren hvid&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694775_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694775_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158694775_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694775_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158694775_detail_en_hd_1.jpg, https://vdxl.im/8721158694775_detail_en_hd_2.jpg, https://vdxl.im/8721158694775_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694775_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ren hvid</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4107391</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8721158694829</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>339</v>
+      </c>
+      <c r="F33" t="n">
+        <v>489</v>
+      </c>
+      <c r="G33" t="n">
+        <v>195</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>35</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694829_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>4107391</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>4107391</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grøn&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694829_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694829_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158694829_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694829_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158694829_detail_en_hd_1.jpg, https://vdxl.im/8721158694829_detail_en_hd_2.jpg, https://vdxl.im/8721158694829_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694829_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>grøn</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>4107396</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8721158694874</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>309</v>
+      </c>
+      <c r="F34" t="n">
+        <v>449</v>
+      </c>
+      <c r="G34" t="n">
+        <v>181</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>32</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694874_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>4107396</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>4107396</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sennepsgul&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694874_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694874_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158694874_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694874_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158694874_detail_en_hd_1.jpg, https://vdxl.im/8721158694874_detail_en_hd_2.jpg, https://vdxl.im/8721158694874_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694874_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>sennepsgul</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4107401</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8721158694928</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>379</v>
+      </c>
+      <c r="F35" t="n">
+        <v>549</v>
+      </c>
+      <c r="G35" t="n">
+        <v>223</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>17</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694928_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>4107401</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>4107401</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lys orange&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694928_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694928_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158694928_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694928_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158694928_detail_en_hd_1.jpg, https://vdxl.im/8721158694928_detail_en_hd_2.jpg, https://vdxl.im/8721158694928_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694928_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lys orange</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>4107406</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8721158694973</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>339</v>
+      </c>
+      <c r="F36" t="n">
+        <v>489</v>
+      </c>
+      <c r="G36" t="n">
+        <v>198</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>40</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694973_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>4107406</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>4107406</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lys pink&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158694973_mo-im_en_hd_1.jpg, https://vdxl.im/8721158694973_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158694973_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158694973_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158694973_detail_en_hd_1.jpg, https://vdxl.im/8721158694973_detail_en_hd_2.jpg, https://vdxl.im/8721158694973_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158694973_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lyserød</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4107411</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8721158695024</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>349</v>
+      </c>
+      <c r="F37" t="n">
+        <v>499</v>
+      </c>
+      <c r="G37" t="n">
+        <v>201</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>144</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158695024_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>4107411</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>4107411</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lyserød&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158695024_mo-im_en_hd_1.jpg, https://vdxl.im/8721158695024_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158695024_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158695024_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158695024_detail_en_hd_1.jpg, https://vdxl.im/8721158695024_detail_en_hd_2.jpg, https://vdxl.im/8721158695024_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158695024_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Baby lyserød</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4107416</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8721158695079</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>289</v>
+      </c>
+      <c r="F38" t="n">
+        <v>419</v>
+      </c>
+      <c r="G38" t="n">
+        <v>169</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>125</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158695079_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>4107416</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>4107416</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Terrakotta&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158695079_mo-im_en_hd_1.jpg, https://vdxl.im/8721158695079_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158695079_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158695079_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158695079_detail_en_hd_1.jpg, https://vdxl.im/8721158695079_detail_en_hd_2.jpg, https://vdxl.im/8721158695079_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158695079_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Terrakotta</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4107421</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8721158695123</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>349</v>
+      </c>
+      <c r="F39" t="n">
+        <v>499</v>
+      </c>
+      <c r="G39" t="n">
+        <v>204</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>30</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158695123_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>4107421</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>4107421</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Turkis&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158695123_mo-im_en_hd_1.jpg, https://vdxl.im/8721158695123_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158695123_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158695123_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158695123_detail_en_hd_1.jpg, https://vdxl.im/8721158695123_detail_en_hd_2.jpg, https://vdxl.im/8721158695123_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158695123_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Turkis</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Øjer</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4107536</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8721158696274</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>269</v>
+      </c>
+      <c r="F40" t="n">
+        <v>389</v>
+      </c>
+      <c r="G40" t="n">
+        <v>158</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>104</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696274_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4107536</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>4107536</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696274_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696274_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158696274_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696274_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158696274_detail_en_hd_1.jpg, https://vdxl.im/8721158696274_detail_en_hd_2.jpg, https://vdxl.im/8721158696274_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696274_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Beige</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4107541</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8721158696328</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>239</v>
+      </c>
+      <c r="F41" t="n">
+        <v>349</v>
+      </c>
+      <c r="G41" t="n">
+        <v>139</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>116</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696328_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>4107541</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>4107541</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696328_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696328_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158696328_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696328_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158696328_detail_en_hd_1.jpg, https://vdxl.im/8721158696328_detail_en_hd_2.jpg, https://vdxl.im/8721158696328_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696328_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4107546</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8721158696373</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>339</v>
+      </c>
+      <c r="F42" t="n">
+        <v>489</v>
+      </c>
+      <c r="G42" t="n">
+        <v>195</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>46</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696373_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4107546</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4107546</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lys blå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696373_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696373_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158696373_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696373_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158696373_detail_en_hd_1.jpg, https://vdxl.im/8721158696373_detail_en_hd_2.jpg, https://vdxl.im/8721158696373_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696373_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lyseblå</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4107551</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8721158696427</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>339</v>
+      </c>
+      <c r="F43" t="n">
+        <v>489</v>
+      </c>
+      <c r="G43" t="n">
+        <v>195</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>62</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696427_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4107551</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4107551</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696427_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696427_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158696427_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696427_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158696427_detail_en_hd_1.jpg, https://vdxl.im/8721158696427_detail_en_hd_2.jpg, https://vdxl.im/8721158696427_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696427_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4107556</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8721158696472</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>309</v>
+      </c>
+      <c r="F44" t="n">
+        <v>449</v>
+      </c>
+      <c r="G44" t="n">
+        <v>180</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>74</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696472_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4107556</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>4107556</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørk brun&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696472_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696472_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158696472_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696472_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158696472_detail_en_hd_1.jpg, https://vdxl.im/8721158696472_detail_en_hd_2.jpg, https://vdxl.im/8721158696472_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696472_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mørkebrun</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4107561</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8721158696526</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>269</v>
+      </c>
+      <c r="F45" t="n">
+        <v>389</v>
+      </c>
+      <c r="G45" t="n">
+        <v>158</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>125</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696526_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4107561</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>4107561</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracit&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696526_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696526_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158696526_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696526_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158696526_detail_en_hd_1.jpg, https://vdxl.im/8721158696526_detail_en_hd_2.jpg, https://vdxl.im/8721158696526_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696526_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Antracit</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4107566</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8721158696571</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>339</v>
+      </c>
+      <c r="F46" t="n">
+        <v>489</v>
+      </c>
+      <c r="G46" t="n">
+        <v>195</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>34</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696571_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4107566</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>4107566</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696571_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696571_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158696571_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696571_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158696571_detail_en_hd_1.jpg, https://vdxl.im/8721158696571_detail_en_hd_2.jpg, https://vdxl.im/8721158696571_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696571_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4107571</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8721158696625</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>339</v>
+      </c>
+      <c r="F47" t="n">
+        <v>489</v>
+      </c>
+      <c r="G47" t="n">
+        <v>195</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>44</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696625_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>4107571</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>4107571</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Bleg grå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696625_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696625_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158696625_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696625_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158696625_detail_en_hd_1.jpg, https://vdxl.im/8721158696625_detail_en_hd_2.jpg, https://vdxl.im/8721158696625_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696625_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lys grå</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>4107576</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8721158696670</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>399</v>
+      </c>
+      <c r="F48" t="n">
+        <v>569</v>
+      </c>
+      <c r="G48" t="n">
+        <v>231</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>8</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696670_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>4107576</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>4107576</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Vinrød&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696670_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696670_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158696670_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696670_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158696670_detail_en_hd_1.jpg, https://vdxl.im/8721158696670_detail_en_hd_2.jpg, https://vdxl.im/8721158696670_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696670_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vinrød</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4107581</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>8721158696724</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>349</v>
+      </c>
+      <c r="F49" t="n">
+        <v>499</v>
+      </c>
+      <c r="G49" t="n">
+        <v>206</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>21</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696724_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>4107581</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>4107581</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Metal grå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696724_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696724_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158696724_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696724_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158696724_detail_en_hd_1.jpg, https://vdxl.im/8721158696724_detail_en_hd_2.jpg, https://vdxl.im/8721158696724_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696724_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Metal grå</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4107586</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>8721158696779</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>399</v>
+      </c>
+      <c r="F50" t="n">
+        <v>569</v>
+      </c>
+      <c r="G50" t="n">
+        <v>235</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>10</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696779_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>4107586</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>4107586</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørk blå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696779_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696779_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158696779_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696779_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158696779_detail_en_hd_1.jpg, https://vdxl.im/8721158696779_detail_en_hd_2.jpg, https://vdxl.im/8721158696779_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696779_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mørkeblå</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>4107591</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8721158696823</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>269</v>
+      </c>
+      <c r="F51" t="n">
+        <v>389</v>
+      </c>
+      <c r="G51" t="n">
+        <v>158</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>95</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696823_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>4107591</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>4107591</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lys brun&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696823_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696823_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158696823_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696823_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158696823_detail_en_hd_1.jpg, https://vdxl.im/8721158696823_detail_en_hd_2.jpg, https://vdxl.im/8721158696823_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696823_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lysebrun</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>4107596</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8721158696878</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>339</v>
+      </c>
+      <c r="F52" t="n">
+        <v>489</v>
+      </c>
+      <c r="G52" t="n">
+        <v>196</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>93</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696878_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>4107596</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>4107596</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696878_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696878_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158696878_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696878_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158696878_detail_en_hd_1.jpg, https://vdxl.im/8721158696878_detail_en_hd_2.jpg, https://vdxl.im/8721158696878_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696878_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4107601</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8721158696922</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>389</v>
+      </c>
+      <c r="F53" t="n">
+        <v>559</v>
+      </c>
+      <c r="G53" t="n">
+        <v>227</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>122</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696922_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4107601</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>4107601</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lilla&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696922_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696922_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158696922_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696922_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158696922_detail_en_hd_1.jpg, https://vdxl.im/8721158696922_detail_en_hd_2.jpg, https://vdxl.im/8721158696922_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696922_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lilla</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>4107606</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8721158696977</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>339</v>
+      </c>
+      <c r="F54" t="n">
+        <v>489</v>
+      </c>
+      <c r="G54" t="n">
+        <v>198</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>51</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696977_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>4107606</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>4107606</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Ren hvid&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158696977_mo-im_en_hd_1.jpg, https://vdxl.im/8721158696977_wbg-fr-m_en_hd_1.jpg, https://vdxl.im/8721158696977_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158696977_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721158696977_detail_en_hd_1.jpg, https://vdxl.im/8721158696977_detail_en_hd_2.jpg, https://vdxl.im/8721158696977_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158696977_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ren hvid</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4107611</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8721158697028</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>339</v>
+      </c>
+      <c r="F55" t="n">
+        <v>489</v>
+      </c>
+      <c r="G55" t="n">
+        <v>195</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>8</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697028_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>4107611</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>4107611</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grøn&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697028_mo-im_en_hd_1.jpg, https://vdxl.im/8721158697028_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158697028_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158697028_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158697028_detail_en_hd_1.jpg, https://vdxl.im/8721158697028_detail_en_hd_2.jpg, https://vdxl.im/8721158697028_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158697028_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>grøn</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>4107616</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>8721158697073</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>449</v>
+      </c>
+      <c r="F56" t="n">
+        <v>649</v>
+      </c>
+      <c r="G56" t="n">
+        <v>262</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>4</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697073_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>4107616</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>4107616</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sennepsgul&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697073_mo-im_en_hd_1.jpg, https://vdxl.im/8721158697073_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158697073_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158697073_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158697073_detail_en_hd_1.jpg, https://vdxl.im/8721158697073_detail_en_hd_2.jpg, https://vdxl.im/8721158697073_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158697073_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>sennepsgul</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>4107621</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>8721158697127</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>399</v>
+      </c>
+      <c r="F57" t="n">
+        <v>569</v>
+      </c>
+      <c r="G57" t="n">
+        <v>231</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697127_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>4107621</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>4107621</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lys orange&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697127_mo-im_en_hd_1.jpg, https://vdxl.im/8721158697127_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158697127_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158697127_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158697127_detail_en_hd_1.jpg, https://vdxl.im/8721158697127_detail_en_hd_2.jpg, https://vdxl.im/8721158697127_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158697127_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lys orange</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>4107626</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>8721158697172</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>379</v>
+      </c>
+      <c r="F58" t="n">
+        <v>549</v>
+      </c>
+      <c r="G58" t="n">
+        <v>220</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>10</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697172_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>4107626</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>4107626</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lys pink&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697172_mo-im_en_hd_1.jpg, https://vdxl.im/8721158697172_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158697172_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158697172_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158697172_detail_en_hd_1.jpg, https://vdxl.im/8721158697172_detail_en_hd_2.jpg, https://vdxl.im/8721158697172_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158697172_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lyserød</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4107631</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>8721158697226</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>409</v>
+      </c>
+      <c r="F59" t="n">
+        <v>589</v>
+      </c>
+      <c r="G59" t="n">
+        <v>240</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>4</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697226_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>4107631</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>4107631</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lyserød&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697226_mo-im_en_hd_1.jpg, https://vdxl.im/8721158697226_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158697226_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158697226_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158697226_detail_en_hd_1.jpg, https://vdxl.im/8721158697226_detail_en_hd_2.jpg, https://vdxl.im/8721158697226_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158697226_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Baby lyserød</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4107636</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>8721158697271</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>339</v>
+      </c>
+      <c r="F60" t="n">
+        <v>489</v>
+      </c>
+      <c r="G60" t="n">
+        <v>195</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>45</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697271_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>4107636</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>4107636</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Terrakotta&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697271_mo-im_en_hd_1.jpg, https://vdxl.im/8721158697271_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158697271_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158697271_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158697271_detail_en_hd_1.jpg, https://vdxl.im/8721158697271_detail_en_hd_2.jpg, https://vdxl.im/8721158697271_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158697271_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Terrakotta</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>moerklaegningsgardiner-med-ringe-2-dele-140-x</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>4107641</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>8721158697325</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>289</v>
+      </c>
+      <c r="F61" t="n">
+        <v>419</v>
+      </c>
+      <c r="G61" t="n">
+        <v>168</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1420</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>139</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697325_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>4107641</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>4107641</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse moderne mørklægningsgardiner er til dig, der gerne vil have en stilfuld, men praktisk løsning til vinduerne. Lavet af polyester og med et smart krog- og ringsystem, så de glider let langs stangen. De er perfekte til stuer, soveværelser og kontorer og tilføjer en cool vibe til ethvert rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Triple vævdesign:&lt;/b&gt; Vores gardiner bruger en smart triple væv teknik, der sikrer et slidstærkt stof og blokerer effektivt for 80%-90% lys. Det er perfekt for dem, der ønsker privatliv uden at mørklægge helt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige hængemuligheder:&lt;/b&gt; Gardinerne kan hænges op med små krog, store krog, bånd eller stanglomme alt efter hvad du foretrækker. Denne fleksibilitet gør dem nemme at tilpasse forskellige stænger og stilarter, så de klæder dit hjem.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel åbningssystem:&lt;/b&gt; Gardinerne har et super enkelt manuelt åbnesystem, der er let at bruge. Krog- og ringsystemet gør det nemt at trække gardinerne for, hvilket giver et flot flow.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Udvendig monteringsmulighed:&lt;/b&gt; De er lavet til at blive hængt uden for vinduesrammen, så de dækker godt og får dine vinduer til at se større ud. De giver også maksimal lyskontrol og privatliv, perfekt til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelsesinstruktioner:&lt;/b&gt; Plejen er simpel, tør dem bare af med en klud. De kan vaskes i maskine ved 40℃, men undgå blegemiddel og tørretumbler. Det gør det nemt at holde dem pæne, selv med daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Turkis&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 245 x 140 cm (L x B)&lt;/li&gt;&lt;li&gt;Vægt: 0,72 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Let i vægt&lt;/li&gt;&lt;li&gt;80%-90% Mørklægning&lt;/li&gt;&lt;li&gt;Triple Vev Design&lt;/li&gt;&lt;li&gt;4 installationsmetoder: Små kroge, store kroge, faner, stanglomme&lt;/li&gt;&lt;li&gt;Bredde på lommeåbningen: 6 cm&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Gardin&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158697325_mo-im_en_hd_1.jpg, https://vdxl.im/8721158697325_wbg-fr-m_en_hd_2.jpg, https://vdxl.im/8721158697325_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721158697325_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721158697325_detail_en_hd_1.jpg, https://vdxl.im/8721158697325_detail_en_hd_2.jpg, https://vdxl.im/8721158697325_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158697325_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Turkis</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>245 cm</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Ophængningsmåder</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Tab tops</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/matrixify_create_large_merge.xlsx
+++ b/output/matrixify_create_large_merge.xlsx
@@ -413,9 +413,2772 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Handle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Variant Command</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Variant SKU</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Variant Barcode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Variant Price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Variant Compare At Price</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Variant Cost</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Variant Weight</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Variant Weight Unit</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Variant Inventory Tracker</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Variant Inventory Policy</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Variant Inventory Qty</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Variant Fulfillment Service</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Variant Requires Shipping</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Variant Taxable</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Variant Image</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Google Shopping / MPN</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Google Shopping / Condition</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Variant Metafield: custom.sku [single_line_text_field]</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Variant Metafield: custom.produktinfo [multi_line_text_field]</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Variant Metafield: custom.variantbilleder [list.single_line_text_field]</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Option1 Name</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Option1 Value</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Option2 Name</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Option2 Value</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Option3 Name</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Option3 Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3372361</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8721288575074</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7699</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>4051</v>
+      </c>
+      <c r="H2" t="n">
+        <v>96220</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575074_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3372361</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3372361</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 144 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Kompatibel madrasstørrelse: Dobbeltseng (140 cm x 200 cm eller 55" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (140 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (140 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (140 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575074_mo-im_en_hd_1.jpg, https://vdxl.im/8721288575074_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288575074_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288575074_mo-im_en_hd_2.jpg, https://vdxl.im/8721288575074_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288575074_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288575074_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288575074_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288575074_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288575074_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288575074_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288575074_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288575074_detail_en_hd_1.jpg, https://vdxl.im/8721288575074_detail_en_hd_2.jpg, https://vdxl.im/8721288575074_detail_en_hd_3.jpg, https://vdxl.im/8721288575074_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288575074_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>140 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Med ensartet mønster</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3372369</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8721288575159</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>7499</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H3" t="n">
+        <v>109940</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>40</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575159_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3372369</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3372369</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Kompatibel madrasstørrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575159_mo-im_en_hd_1.jpg, https://vdxl.im/8721288575159_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288575159_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288575159_mo-im_en_hd_2.jpg, https://vdxl.im/8721288575159_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288575159_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288575159_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288575159_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288575159_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288575159_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288575159_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288575159_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288575159_detail_en_hd_1.jpg, https://vdxl.im/8721288575159_detail_en_hd_2.jpg, https://vdxl.im/8721288575159_detail_en_hd_3.jpg, https://vdxl.im/8721288575159_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288575159_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Med ensartet mønster</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3372370</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8721288575166</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>7699</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>4052</v>
+      </c>
+      <c r="H4" t="n">
+        <v>110240</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575166_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3372370</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3372370</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Kompatibel madrasstørrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575166_mo-im_en_hd_1.jpg, https://vdxl.im/8721288575166_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288575166_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288575166_mo-im_en_hd_2.jpg, https://vdxl.im/8721288575166_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288575166_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288575166_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288575166_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288575166_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288575166_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288575166_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288575166_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288575166_detail_en_hd_1.jpg, https://vdxl.im/8721288575166_detail_en_hd_2.jpg, https://vdxl.im/8721288575166_detail_en_hd_3.jpg, https://vdxl.im/8721288575166_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288575166_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Med ensartet mønster</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3372371</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8721288575173</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>7699</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>4074</v>
+      </c>
+      <c r="H5" t="n">
+        <v>111040</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>37</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575173_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3372371</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3372371</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Kompatibel madrasstørrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575173_mo-im_en_hd_1.jpg, https://vdxl.im/8721288575173_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288575173_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288575173_mo-im_en_hd_2.jpg, https://vdxl.im/8721288575173_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288575173_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288575173_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288575173_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288575173_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288575173_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288575173_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288575173_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288575173_detail_en_hd_1.jpg, https://vdxl.im/8721288575173_detail_en_hd_2.jpg, https://vdxl.im/8721288575173_detail_en_hd_3.jpg, https://vdxl.im/8721288575173_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288575173_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Med ensartet mønster</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3372372</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8721288575180</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>7999</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>4230</v>
+      </c>
+      <c r="H6" t="n">
+        <v>110240</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575180_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3372372</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3372372</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Kompatibel madrasstørrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575180_mo-im_en_hd_1.jpg, https://vdxl.im/8721288575180_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288575180_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288575180_mo-im_en_hd_2.jpg, https://vdxl.im/8721288575180_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288575180_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288575180_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288575180_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288575180_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288575180_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288575180_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288575180_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288575180_detail_en_hd_1.jpg, https://vdxl.im/8721288575180_detail_en_hd_2.jpg, https://vdxl.im/8721288575180_detail_en_hd_3.jpg, https://vdxl.im/8721288575180_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288575180_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Med ensartet mønster</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3372373</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8721288575197</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>7799</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>4102</v>
+      </c>
+      <c r="H7" t="n">
+        <v>110340</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575197_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3372373</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3372373</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Kompatibel madrasstørrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575197_mo-im_en_hd_1.jpg, https://vdxl.im/8721288575197_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288575197_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288575197_mo-im_en_hd_2.jpg, https://vdxl.im/8721288575197_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288575197_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288575197_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288575197_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288575197_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288575197_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288575197_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288575197_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288575197_detail_en_hd_1.jpg, https://vdxl.im/8721288575197_detail_en_hd_2.jpg, https://vdxl.im/8721288575197_detail_en_hd_3.jpg, https://vdxl.im/8721288575197_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288575197_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Med ensartet mønster</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3372374</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8721288575203</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>7799</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>4107</v>
+      </c>
+      <c r="H8" t="n">
+        <v>110240</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575203_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3372374</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3372374</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Kompatibel madrasstørrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288575203_mo-im_en_hd_1.jpg, https://vdxl.im/8721288575203_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288575203_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288575203_mo-im_en_hd_2.jpg, https://vdxl.im/8721288575203_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288575203_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288575203_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288575203_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288575203_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288575203_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288575203_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288575203_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288575203_detail_en_hd_1.jpg, https://vdxl.im/8721288575203_detail_en_hd_2.jpg, https://vdxl.im/8721288575203_detail_en_hd_3.jpg, https://vdxl.im/8721288575203_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288575203_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Med ensartet mønster</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3372487</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8721288576330</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>7699</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>4067</v>
+      </c>
+      <c r="H9" t="n">
+        <v>97020</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576330_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3372487</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3372487</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 144 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Dobbeltseng (140 cm x 200 cm eller 55" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (140 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (140 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (140 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576330_mo-im_en_hd_1.jpg, https://vdxl.im/8721288576330_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288576330_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288576330_mo-im_en_hd_2.jpg, https://vdxl.im/8721288576330_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288576330_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288576330_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288576330_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288576330_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288576330_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288576330_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288576330_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288576330_detail_en_hd_1.jpg, https://vdxl.im/8721288576330_detail_en_hd_2.jpg, https://vdxl.im/8721288576330_detail_en_hd_3.jpg, https://vdxl.im/8721288576330_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288576330_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>140 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Quilted design</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3372495</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8721288576415</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>7799</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>4104</v>
+      </c>
+      <c r="H10" t="n">
+        <v>111140</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>45</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576415_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3372495</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3372495</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576415_mo-im_en_hd_1.jpg, https://vdxl.im/8721288576415_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288576415_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288576415_mo-im_en_hd_2.jpg, https://vdxl.im/8721288576415_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288576415_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288576415_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288576415_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288576415_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288576415_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288576415_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288576415_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288576415_detail_en_hd_1.jpg, https://vdxl.im/8721288576415_detail_en_hd_2.jpg, https://vdxl.im/8721288576415_detail_en_hd_3.jpg, https://vdxl.im/8721288576415_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288576415_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Quilted design</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3372496</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8721288576422</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>7749</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>4090</v>
+      </c>
+      <c r="H11" t="n">
+        <v>111440</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>63</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576422_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3372496</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3372496</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576422_mo-im_en_hd_1.jpg, https://vdxl.im/8721288576422_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288576422_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288576422_mo-im_en_hd_2.jpg, https://vdxl.im/8721288576422_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288576422_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288576422_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288576422_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288576422_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288576422_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288576422_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288576422_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288576422_detail_en_hd_1.jpg, https://vdxl.im/8721288576422_detail_en_hd_2.jpg, https://vdxl.im/8721288576422_detail_en_hd_3.jpg, https://vdxl.im/8721288576422_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288576422_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Quilted design</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3372497</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8721288576439</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>8149</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>4305</v>
+      </c>
+      <c r="H12" t="n">
+        <v>112240</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>38</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576439_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3372497</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3372497</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576439_mo-im_en_hd_1.jpg, https://vdxl.im/8721288576439_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288576439_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288576439_mo-im_en_hd_2.jpg, https://vdxl.im/8721288576439_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288576439_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288576439_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288576439_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288576439_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288576439_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288576439_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288576439_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288576439_detail_en_hd_1.jpg, https://vdxl.im/8721288576439_detail_en_hd_2.jpg, https://vdxl.im/8721288576439_detail_en_hd_3.jpg, https://vdxl.im/8721288576439_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288576439_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Quilted design</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3372498</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8721288576446</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>8049</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>4256</v>
+      </c>
+      <c r="H13" t="n">
+        <v>111440</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>12</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576446_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3372498</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3372498</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576446_mo-im_en_hd_1.jpg, https://vdxl.im/8721288576446_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288576446_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288576446_mo-im_en_hd_2.jpg, https://vdxl.im/8721288576446_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288576446_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288576446_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288576446_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288576446_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288576446_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288576446_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288576446_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288576446_detail_en_hd_1.jpg, https://vdxl.im/8721288576446_detail_en_hd_2.jpg, https://vdxl.im/8721288576446_detail_en_hd_3.jpg, https://vdxl.im/8721288576446_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288576446_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Quilted design</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3372499</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8721288576453</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>8099</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>4276</v>
+      </c>
+      <c r="H14" t="n">
+        <v>111540</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576453_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3372499</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3372499</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576453_mo-im_en_hd_1.jpg, https://vdxl.im/8721288576453_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288576453_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288576453_mo-im_en_hd_2.jpg, https://vdxl.im/8721288576453_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288576453_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288576453_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288576453_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288576453_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288576453_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288576453_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288576453_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288576453_detail_en_hd_1.jpg, https://vdxl.im/8721288576453_detail_en_hd_2.jpg, https://vdxl.im/8721288576453_detail_en_hd_3.jpg, https://vdxl.im/8721288576453_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288576453_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Quilted design</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3372500</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8721288576460</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>8249</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>4354</v>
+      </c>
+      <c r="H15" t="n">
+        <v>111440</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>9</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576460_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3372500</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3372500</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Kompatibel madrasstørrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576460_mo-im_en_hd_1.jpg, https://vdxl.im/8721288576460_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288576460_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288576460_mo-im_en_hd_2.jpg, https://vdxl.im/8721288576460_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288576460_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288576460_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288576460_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288576460_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288576460_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288576460_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288576460_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288576460_detail_en_hd_1.jpg, https://vdxl.im/8721288576460_detail_en_hd_2.jpg, https://vdxl.im/8721288576460_detail_en_hd_3.jpg, https://vdxl.im/8721288576460_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288576460_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Quilted design</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3372550</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8721288576965</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>7649</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>4041</v>
+      </c>
+      <c r="H16" t="n">
+        <v>95920</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576965_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3372550</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3372550</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 144 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Kompatibel madrasstørrelse: Dobbeltseng (140 cm x 200 cm eller 55" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (140 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (140 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (140 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288576965_mo-im_en_hd_1.jpg, https://vdxl.im/8721288576965_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288576965_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288576965_mo-im_en_hd_2.jpg, https://vdxl.im/8721288576965_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288576965_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288576965_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288576965_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288576965_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288576965_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288576965_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288576965_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288576965_detail_en_hd_1.jpg, https://vdxl.im/8721288576965_detail_en_hd_2.jpg, https://vdxl.im/8721288576965_detail_en_hd_3.jpg, https://vdxl.im/8721288576965_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288576965_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>140 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Knapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3372558</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8721288577047</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>7699</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>4056</v>
+      </c>
+      <c r="H17" t="n">
+        <v>110340</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>45</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577047_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3372558</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3372558</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577047_mo-im_en_hd_1.jpg, https://vdxl.im/8721288577047_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288577047_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288577047_mo-im_en_hd_2.jpg, https://vdxl.im/8721288577047_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288577047_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288577047_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288577047_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288577047_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288577047_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288577047_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288577047_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288577047_detail_en_hd_1.jpg, https://vdxl.im/8721288577047_detail_en_hd_2.jpg, https://vdxl.im/8721288577047_detail_en_hd_3.jpg, https://vdxl.im/8721288577047_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288577047_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Knapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3372559</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8721288577054</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>7749</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>4100</v>
+      </c>
+      <c r="H18" t="n">
+        <v>110640</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>48</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577054_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3372559</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3372559</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577054_mo-im_en_hd_1.jpg, https://vdxl.im/8721288577054_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288577054_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288577054_mo-im_en_hd_2.jpg, https://vdxl.im/8721288577054_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288577054_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288577054_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288577054_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288577054_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288577054_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288577054_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288577054_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288577054_detail_en_hd_1.jpg, https://vdxl.im/8721288577054_detail_en_hd_2.jpg, https://vdxl.im/8721288577054_detail_en_hd_3.jpg, https://vdxl.im/8721288577054_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288577054_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Knapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3372560</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8721288577061</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>7799</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>4119</v>
+      </c>
+      <c r="H19" t="n">
+        <v>111440</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>27</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577061_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3372560</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3372560</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577061_mo-im_en_hd_1.jpg, https://vdxl.im/8721288577061_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288577061_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288577061_mo-im_en_hd_2.jpg, https://vdxl.im/8721288577061_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288577061_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288577061_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288577061_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288577061_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288577061_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288577061_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288577061_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288577061_detail_en_hd_1.jpg, https://vdxl.im/8721288577061_detail_en_hd_2.jpg, https://vdxl.im/8721288577061_detail_en_hd_3.jpg, https://vdxl.im/8721288577061_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288577061_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Knapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3372561</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8721288577078</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>7949</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>4205</v>
+      </c>
+      <c r="H20" t="n">
+        <v>110640</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>13</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577078_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3372561</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>3372561</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577078_mo-im_en_hd_1.jpg, https://vdxl.im/8721288577078_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288577078_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288577078_mo-im_en_hd_2.jpg, https://vdxl.im/8721288577078_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288577078_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288577078_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288577078_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288577078_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288577078_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288577078_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288577078_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288577078_detail_en_hd_1.jpg, https://vdxl.im/8721288577078_detail_en_hd_2.jpg, https://vdxl.im/8721288577078_detail_en_hd_3.jpg, https://vdxl.im/8721288577078_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288577078_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Knapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3372562</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8721288577085</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>7899</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>4154</v>
+      </c>
+      <c r="H21" t="n">
+        <v>110740</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577085_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3372562</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>3372562</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577085_mo-im_en_hd_1.jpg, https://vdxl.im/8721288577085_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288577085_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288577085_mo-im_en_hd_2.jpg, https://vdxl.im/8721288577085_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288577085_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288577085_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288577085_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288577085_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288577085_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288577085_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288577085_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288577085_detail_en_hd_1.jpg, https://vdxl.im/8721288577085_detail_en_hd_2.jpg, https://vdxl.im/8721288577085_detail_en_hd_3.jpg, https://vdxl.im/8721288577085_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288577085_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Knapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>seng-med-opbevaring-og-led-polyester</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3372563</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8721288577092</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>7649</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>4029</v>
+      </c>
+      <c r="H22" t="n">
+        <v>110640</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>9</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577092_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>3372563</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>3372563</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne moderne opbevaringsseng med madras har et strømlinet design og smarte funktioner, der giver et elegant touch til dit soveværelse. Med sin rektangulære form og enkle linjer skaber sengen en moderne stemning og er super praktisk. Den flotte stil fremhæves af LED-strips, der tilføjer en fin stemning. Perfekt for dem der vil have både stil og opbevaring, er denne seng et virkelig godt midtpunkt i ethvert soveværelse, hvor den giver både bekvemmelighed og elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengen og støtteelementerne er lavet af holdbart metal, hvilket sikrer god holdbarhed til dagligt brug. Madrassen og hovedgærdet er dækket i kvalitets polyester, der både ser godt ud og er nemt at holde rent.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengen kommer med en medium-fast madras, der passer til flere måde at sove på. Hovedgærdet, betrukket med blødt polyester, er komfortabelt, og den indbyggede LED-belysning sætter stemningen og gør sengen unik.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hydraulisk løftopbevaring:&lt;/b&gt; Med den hydrauliske mekanisme har du masser af opbevaringsplads under sengen. Det er en super praktisk funktion for dem, der har brug for lidt ekstra plads, da det er nemt at holde orden. De holdbare mekanismer sikrer langvarig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;LED-belysning:&lt;/b&gt; LED-strips på hovedgærdet giver dig mange muligheder for at vælge den rigtige belysning. Du kan tilpasse det efter humøret eller indretningen i dit værelse, og de bruger en USB-forbindelse, hvilket er smart og energibesparende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde sengen pæn, skal du blot tørre polyesterfladerne med en tør klud. Hold alt elektronisk udstyr tørt og støvfrit for at forlænge levetiden. Minimal pleje beskytter din seng i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Polyester&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 204 x 180 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Madras størrelse: Super king seng (180 cm x 200 cm eller 71" x 79")&lt;/li&gt;&lt;li&gt;Maks. vægt: 200 kg&lt;/li&gt;&lt;li&gt;Maksimalt antal mennesker: 2&lt;/li&gt;&lt;li&gt;Sengens højde: 48,5 cm&lt;/li&gt;&lt;li&gt;Rigelig opbevaring under sengen&lt;/li&gt;&lt;li&gt;Hydraulisk side løftmekanisme&lt;/li&gt;&lt;li&gt;Med RGB LED&lt;/li&gt;&lt;li&gt;Med lamelramme&lt;/li&gt;&lt;li&gt;Med madras&lt;/li&gt;&lt;li&gt;Med sengegavl&lt;/li&gt;&lt;li&gt;Med LED&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x seng (180 x 204 cm)&lt;/li&gt;&lt;li&gt;1 x madras (180 x 200 x 20 cm)&lt;/li&gt;&lt;li&gt;1 x madras-topper (180 x 200 x 5 cm)&lt;/li&gt;&lt;li&gt;1 x hovedgærde&lt;/li&gt;&lt;li&gt;2 x LED-stripe&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288577092_mo-im_en_hd_1.jpg, https://vdxl.im/8721288577092_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288577092_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288577092_mo-im_en_hd_2.jpg, https://vdxl.im/8721288577092_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288577092_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288577092_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288577092_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288577092_wbg-fr_en_hd_2.jpg, https://vdxl.im/8721288577092_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288577092_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288577092_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288577092_detail_en_hd_1.jpg, https://vdxl.im/8721288577092_detail_en_hd_2.jpg, https://vdxl.im/8721288577092_detail_en_hd_3.jpg, https://vdxl.im/8721288577092_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288577092_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Knapper</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>